--- a/eval/results/evaluation_metrics_full150.xlsx
+++ b/eval/results/evaluation_metrics_full150.xlsx
@@ -486,25 +486,25 @@
         <v>2400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7440100882723834</v>
+        <v>0.7477820025348543</v>
       </c>
       <c r="D2" t="n">
         <v>0.6014271151885831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.665163472378805</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F2" t="n">
         <v>590</v>
       </c>
       <c r="G2" t="n">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="H2" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I2" t="n">
         <v>391</v>
@@ -520,28 +520,28 @@
         <v>2400</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8204166666666667</v>
+        <v>0.8216666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8168202764976958</v>
+        <v>0.8203939745075318</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7227319062181448</v>
+        <v>0.7217125382262997</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7669010275824769</v>
+        <v>0.7678958785249458</v>
       </c>
       <c r="F3" t="n">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G3" t="n">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="H3" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
         <v>2400</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7191666666666666</v>
+        <v>0.7175</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6750285062713797</v>
+        <v>0.6711864406779661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6034658511722731</v>
+        <v>0.6055045871559633</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6372443487621098</v>
+        <v>0.6366559485530546</v>
       </c>
       <c r="F5" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G5" t="n">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="H5" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I5" t="n">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -622,28 +622,28 @@
         <v>2400</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.7891666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8624813153961136</v>
+        <v>0.8487518355359766</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5881753312945973</v>
+        <v>0.5891946992864424</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6993939393939393</v>
+        <v>0.6955475330926595</v>
       </c>
       <c r="F6" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G6" t="n">
-        <v>1327</v>
+        <v>1316</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -724,28 +724,28 @@
         <v>2400</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7454166666666666</v>
+        <v>0.7441666666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8104026845637584</v>
+        <v>0.8023064250411862</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4923547400611621</v>
+        <v>0.4964322120285423</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6125554850982879</v>
+        <v>0.6133501259445845</v>
       </c>
       <c r="F9" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G9" t="n">
-        <v>1306</v>
+        <v>1299</v>
       </c>
       <c r="H9" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I9" t="n">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -758,28 +758,28 @@
         <v>2400</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7045833333333333</v>
+        <v>0.6975</v>
       </c>
       <c r="C10" t="n">
-        <v>0.630019120458891</v>
+        <v>0.6186046511627907</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6717635066258919</v>
+        <v>0.6778797145769623</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6502220029600394</v>
+        <v>0.6468871595330739</v>
       </c>
       <c r="F10" t="n">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G10" t="n">
-        <v>1032</v>
+        <v>1009</v>
       </c>
       <c r="H10" t="n">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="I10" t="n">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -858,25 +858,25 @@
         <v>2400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7440100882723834</v>
+        <v>0.7477820025348543</v>
       </c>
       <c r="D2" t="n">
         <v>0.6014271151885831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.665163472378805</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F2" t="n">
         <v>590</v>
       </c>
       <c r="G2" t="n">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="H2" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I2" t="n">
         <v>391</v>
@@ -892,28 +892,28 @@
         <v>2400</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8204166666666667</v>
+        <v>0.8216666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8168202764976958</v>
+        <v>0.8203939745075318</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7227319062181448</v>
+        <v>0.7217125382262997</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7669010275824769</v>
+        <v>0.7678958785249458</v>
       </c>
       <c r="F3" t="n">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G3" t="n">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="H3" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         <v>2400</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7191666666666666</v>
+        <v>0.7175</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6750285062713797</v>
+        <v>0.6711864406779661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6034658511722731</v>
+        <v>0.6055045871559633</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6372443487621098</v>
+        <v>0.6366559485530546</v>
       </c>
       <c r="F5" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G5" t="n">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="H5" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I5" t="n">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -994,28 +994,28 @@
         <v>2400</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.7891666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8624813153961136</v>
+        <v>0.8487518355359766</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5881753312945973</v>
+        <v>0.5891946992864424</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6993939393939393</v>
+        <v>0.6955475330926595</v>
       </c>
       <c r="F6" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G6" t="n">
-        <v>1327</v>
+        <v>1316</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1096,28 +1096,28 @@
         <v>2400</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7454166666666666</v>
+        <v>0.7441666666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8104026845637584</v>
+        <v>0.8023064250411862</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4923547400611621</v>
+        <v>0.4964322120285423</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6125554850982879</v>
+        <v>0.6133501259445845</v>
       </c>
       <c r="F9" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G9" t="n">
-        <v>1306</v>
+        <v>1299</v>
       </c>
       <c r="H9" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I9" t="n">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1130,28 +1130,28 @@
         <v>2400</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7045833333333333</v>
+        <v>0.6975</v>
       </c>
       <c r="C10" t="n">
-        <v>0.630019120458891</v>
+        <v>0.6186046511627907</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6717635066258919</v>
+        <v>0.6778797145769623</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6502220029600394</v>
+        <v>0.6468871595330739</v>
       </c>
       <c r="F10" t="n">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G10" t="n">
-        <v>1032</v>
+        <v>1009</v>
       </c>
       <c r="H10" t="n">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="I10" t="n">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics_full150.xlsx
+++ b/eval/results/evaluation_metrics_full150.xlsx
@@ -486,28 +486,28 @@
         <v>2400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.8220833333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7477820025348543</v>
+        <v>0.8397790055248618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6014271151885831</v>
+        <v>0.7293666026871402</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7806882383153571</v>
       </c>
       <c r="F2" t="n">
-        <v>590</v>
+        <v>760</v>
       </c>
       <c r="G2" t="n">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="H2" t="n">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="I2" t="n">
-        <v>391</v>
+        <v>282</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -520,28 +520,28 @@
         <v>2400</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8216666666666667</v>
+        <v>0.89125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8203939745075318</v>
+        <v>0.90216271884655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7217125382262997</v>
+        <v>0.8406909788867563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7678958785249458</v>
+        <v>0.8703427719821163</v>
       </c>
       <c r="F3" t="n">
-        <v>708</v>
+        <v>876</v>
       </c>
       <c r="G3" t="n">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H3" t="n">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,28 +554,28 @@
         <v>2400</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8566666666666667</v>
+        <v>0.8429166666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8349106203995794</v>
+        <v>0.8348439073514602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8093781855249745</v>
+        <v>0.7955854126679462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8219461697722568</v>
+        <v>0.8147420147420148</v>
       </c>
       <c r="F4" t="n">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="G4" t="n">
-        <v>1262</v>
+        <v>1194</v>
       </c>
       <c r="H4" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I4" t="n">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
         <v>2400</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7175</v>
+        <v>0.7945833333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6711864406779661</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6055045871559633</v>
+        <v>0.7428023032629558</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6366559485530546</v>
+        <v>0.758451739343459</v>
       </c>
       <c r="F5" t="n">
-        <v>594</v>
+        <v>774</v>
       </c>
       <c r="G5" t="n">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="H5" t="n">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="I5" t="n">
-        <v>387</v>
+        <v>268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -622,28 +622,28 @@
         <v>2400</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7891666666666667</v>
+        <v>0.8470833333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8487518355359766</v>
+        <v>0.9343629343629344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5891946992864424</v>
+        <v>0.6967370441458733</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6955475330926595</v>
+        <v>0.7982407916437604</v>
       </c>
       <c r="F6" t="n">
-        <v>578</v>
+        <v>726</v>
       </c>
       <c r="G6" t="n">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="H6" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="I6" t="n">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -656,28 +656,28 @@
         <v>2400</v>
       </c>
       <c r="B7" t="n">
-        <v>0.795</v>
+        <v>0.8683333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7859649122807018</v>
+        <v>0.8773388773388774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6850152905198776</v>
+        <v>0.8099808061420346</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7320261437908497</v>
+        <v>0.8423153692614772</v>
       </c>
       <c r="F7" t="n">
-        <v>672</v>
+        <v>844</v>
       </c>
       <c r="G7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="H7" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="I7" t="n">
-        <v>309</v>
+        <v>198</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -690,28 +690,28 @@
         <v>2400</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7279166666666667</v>
+        <v>0.7758333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7124352331606217</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5606523955147809</v>
+        <v>0.6525911708253359</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6274957216200798</v>
+        <v>0.7165437302423603</v>
       </c>
       <c r="F8" t="n">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="G8" t="n">
-        <v>1197</v>
+        <v>1182</v>
       </c>
       <c r="H8" t="n">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="I8" t="n">
-        <v>431</v>
+        <v>362</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -724,28 +724,28 @@
         <v>2400</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7441666666666666</v>
+        <v>0.7841666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8023064250411862</v>
+        <v>0.8797101449275362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4964322120285423</v>
+        <v>0.5825335892514395</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6133501259445845</v>
+        <v>0.7009237875288683</v>
       </c>
       <c r="F9" t="n">
-        <v>487</v>
+        <v>607</v>
       </c>
       <c r="G9" t="n">
-        <v>1299</v>
+        <v>1275</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="I9" t="n">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -758,28 +758,28 @@
         <v>2400</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6975</v>
+        <v>0.7795833333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6186046511627907</v>
+        <v>0.7107641741988496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6778797145769623</v>
+        <v>0.8301343570057581</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6468871595330739</v>
+        <v>0.7658255865427179</v>
       </c>
       <c r="F10" t="n">
-        <v>665</v>
+        <v>865</v>
       </c>
       <c r="G10" t="n">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="H10" t="n">
-        <v>410</v>
+        <v>352</v>
       </c>
       <c r="I10" t="n">
-        <v>316</v>
+        <v>177</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -858,28 +858,28 @@
         <v>2400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7541666666666667</v>
+        <v>0.8220833333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7477820025348543</v>
+        <v>0.8397790055248618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6014271151885831</v>
+        <v>0.7293666026871402</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7806882383153571</v>
       </c>
       <c r="F2" t="n">
-        <v>590</v>
+        <v>760</v>
       </c>
       <c r="G2" t="n">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="H2" t="n">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="I2" t="n">
-        <v>391</v>
+        <v>282</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -892,28 +892,28 @@
         <v>2400</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8216666666666667</v>
+        <v>0.89125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8203939745075318</v>
+        <v>0.90216271884655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7217125382262997</v>
+        <v>0.8406909788867563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7678958785249458</v>
+        <v>0.8703427719821163</v>
       </c>
       <c r="F3" t="n">
-        <v>708</v>
+        <v>876</v>
       </c>
       <c r="G3" t="n">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H3" t="n">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -926,28 +926,28 @@
         <v>2400</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8566666666666667</v>
+        <v>0.8429166666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8349106203995794</v>
+        <v>0.8348439073514602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8093781855249745</v>
+        <v>0.7955854126679462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8219461697722568</v>
+        <v>0.8147420147420148</v>
       </c>
       <c r="F4" t="n">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="G4" t="n">
-        <v>1262</v>
+        <v>1194</v>
       </c>
       <c r="H4" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I4" t="n">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         <v>2400</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7175</v>
+        <v>0.7945833333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6711864406779661</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6055045871559633</v>
+        <v>0.7428023032629558</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6366559485530546</v>
+        <v>0.758451739343459</v>
       </c>
       <c r="F5" t="n">
-        <v>594</v>
+        <v>774</v>
       </c>
       <c r="G5" t="n">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="H5" t="n">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="I5" t="n">
-        <v>387</v>
+        <v>268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -994,28 +994,28 @@
         <v>2400</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7891666666666667</v>
+        <v>0.8470833333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8487518355359766</v>
+        <v>0.9343629343629344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5891946992864424</v>
+        <v>0.6967370441458733</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6955475330926595</v>
+        <v>0.7982407916437604</v>
       </c>
       <c r="F6" t="n">
-        <v>578</v>
+        <v>726</v>
       </c>
       <c r="G6" t="n">
-        <v>1316</v>
+        <v>1307</v>
       </c>
       <c r="H6" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="I6" t="n">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1028,28 +1028,28 @@
         <v>2400</v>
       </c>
       <c r="B7" t="n">
-        <v>0.795</v>
+        <v>0.8683333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7859649122807018</v>
+        <v>0.8773388773388774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6850152905198776</v>
+        <v>0.8099808061420346</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7320261437908497</v>
+        <v>0.8423153692614772</v>
       </c>
       <c r="F7" t="n">
-        <v>672</v>
+        <v>844</v>
       </c>
       <c r="G7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="H7" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="I7" t="n">
-        <v>309</v>
+        <v>198</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1062,28 +1062,28 @@
         <v>2400</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7279166666666667</v>
+        <v>0.7758333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7124352331606217</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5606523955147809</v>
+        <v>0.6525911708253359</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6274957216200798</v>
+        <v>0.7165437302423603</v>
       </c>
       <c r="F8" t="n">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="G8" t="n">
-        <v>1197</v>
+        <v>1182</v>
       </c>
       <c r="H8" t="n">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="I8" t="n">
-        <v>431</v>
+        <v>362</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1096,28 +1096,28 @@
         <v>2400</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7441666666666666</v>
+        <v>0.7841666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8023064250411862</v>
+        <v>0.8797101449275362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4964322120285423</v>
+        <v>0.5825335892514395</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6133501259445845</v>
+        <v>0.7009237875288683</v>
       </c>
       <c r="F9" t="n">
-        <v>487</v>
+        <v>607</v>
       </c>
       <c r="G9" t="n">
-        <v>1299</v>
+        <v>1275</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="I9" t="n">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1130,28 +1130,28 @@
         <v>2400</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6975</v>
+        <v>0.7795833333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6186046511627907</v>
+        <v>0.7107641741988496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6778797145769623</v>
+        <v>0.8301343570057581</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6468871595330739</v>
+        <v>0.7658255865427179</v>
       </c>
       <c r="F10" t="n">
-        <v>665</v>
+        <v>865</v>
       </c>
       <c r="G10" t="n">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="H10" t="n">
-        <v>410</v>
+        <v>352</v>
       </c>
       <c r="I10" t="n">
-        <v>316</v>
+        <v>177</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
